--- a/testdata/realdata/leased_lines.xlsx
+++ b/testdata/realdata/leased_lines.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>协议带宽</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +578,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +620,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,6 +662,11 @@
           <t>1000</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>在建</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -672,6 +702,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>1000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
